--- a/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,52</t>
+          <t>1,62; 10,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,99</t>
+          <t>1,23; 11,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 15,99</t>
+          <t>3,25; 15,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 10,01</t>
+          <t>2,51; 9,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 11,79</t>
+          <t>2,78; 12,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 6,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,89</t>
+          <t>0,0; 6,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,6</t>
+          <t>1,2; 6,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,75</t>
+          <t>2,47; 8,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,75</t>
+          <t>1,52; 6,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,5</t>
+          <t>2,52; 9,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,55</t>
+          <t>2,22; 7,08</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,89</t>
+          <t>0,97; 8,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 16,3</t>
+          <t>3,33; 15,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 13,54</t>
+          <t>3,36; 12,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 8,41</t>
+          <t>1,14; 9,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 16,09</t>
+          <t>4,09; 15,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 12,05</t>
+          <t>2,85; 13,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,86</t>
+          <t>2,22; 10,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 11,02</t>
+          <t>2,47; 11,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 10,68</t>
+          <t>3,45; 9,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 11,74</t>
+          <t>3,9; 11,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,21</t>
+          <t>3,39; 9,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,81</t>
+          <t>2,35; 8,16</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,23</t>
+          <t>1,34; 11,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 20,05</t>
+          <t>6,63; 20,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 19,87</t>
+          <t>4,37; 19,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 17,5</t>
+          <t>3,62; 17,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,37</t>
+          <t>1,56; 9,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 16,62</t>
+          <t>4,23; 16,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,52</t>
+          <t>1,34; 10,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 7,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,13</t>
+          <t>2,39; 8,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 15,29</t>
+          <t>6,47; 15,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 12,43</t>
+          <t>3,61; 11,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 9,18</t>
+          <t>2,44; 9,73</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,43</t>
+          <t>2,33; 8,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,07; 16,5</t>
+          <t>7,66; 16,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 12,47</t>
+          <t>4,95; 11,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,85</t>
+          <t>1,98; 6,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,21</t>
+          <t>2,58; 8,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 14,27</t>
+          <t>6,22; 13,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,0</t>
+          <t>4,25; 10,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 14,37</t>
+          <t>5,97; 14,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,26</t>
+          <t>3,13; 7,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 13,93</t>
+          <t>8,08; 13,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,39</t>
+          <t>5,32; 10,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 9,41</t>
+          <t>4,26; 9,45</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 20,94</t>
+          <t>7,58; 20,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 16,49</t>
+          <t>5,9; 16,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,79</t>
+          <t>7,15; 16,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,12; 16,63</t>
+          <t>6,79; 16,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,47; 22,75</t>
+          <t>10,06; 22,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 22,53</t>
+          <t>9,49; 22,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 20,58</t>
+          <t>9,17; 20,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 16,54</t>
+          <t>6,76; 16,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 19,87</t>
+          <t>9,79; 18,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,58; 16,78</t>
+          <t>8,46; 17,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,08; 16,57</t>
+          <t>8,97; 16,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 14,53</t>
+          <t>7,9; 14,93</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,12; 17,96</t>
+          <t>5,7; 17,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 22,42</t>
+          <t>6,79; 22,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 13,65</t>
+          <t>2,47; 13,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,49</t>
+          <t>2,85; 12,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,62; 17,86</t>
+          <t>6,2; 18,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,91; 20,03</t>
+          <t>6,61; 19,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,88</t>
+          <t>0,98; 9,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,38; 25,1</t>
+          <t>8,79; 24,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,04; 15,48</t>
+          <t>7,17; 15,36</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,13; 17,76</t>
+          <t>8,45; 18,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 9,52</t>
+          <t>2,66; 9,16</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,6; 16,87</t>
+          <t>7,03; 16,79</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,49</t>
+          <t>4,94; 8,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,53</t>
+          <t>8,05; 12,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 10,66</t>
+          <t>6,83; 11,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,79</t>
+          <t>4,37; 7,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,94</t>
+          <t>6,36; 10,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 11,32</t>
+          <t>7,47; 11,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,47</t>
+          <t>4,93; 8,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,07</t>
+          <t>6,47; 10,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,67</t>
+          <t>6,06; 8,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,31</t>
+          <t>8,15; 11,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,38; 8,83</t>
+          <t>6,25; 9,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 8,55</t>
+          <t>5,88; 8,41</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3494</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2990</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5235</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5377</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4163</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4350</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7658</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4409</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6851</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>9726</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1305; 8224</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>750; 6929</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2105; 9731</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2605; 10307</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1990; 9035</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4908</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5138</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1628; 8954</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3755; 12668</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2042; 9178</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3599; 12873</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5329; 16977</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2651</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5865</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3139</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5761</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4272</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4591</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5343</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8412</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9452</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10456</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8482</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>665; 5943</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2175; 9976</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2764; 10422</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1075; 9016</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2762; 10690</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1952; 9211</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2049; 9541</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2341; 11128</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4699; 13395</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5227; 15348</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5916; 16634</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4444; 15432</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2849</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7768</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5055</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3879</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2911</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6728</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13842</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7966</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>5790</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>783; 6739</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4411; 13367</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2153; 9623</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1790; 8745</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1306; 8084</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2873; 11238</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>817; 6549</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4634</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3395; 12329</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8703; 21035</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3982; 13175</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2759; 11019</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6987</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15960</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13149</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8335</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7324</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15670</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12068</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>20224</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14311</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>31630</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25217</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>28559</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3513; 12468</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10457; 22582</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8206; 19507</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4305; 14653</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3832; 12218</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10038; 22487</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7265; 18451</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>13027; 31144</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9356; 21544</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>24060; 40682</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>17906; 33905</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>18540; 41121</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8963</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9455</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11358</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13075</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>13056</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13273</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13752</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>17685</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>22018</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22728</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>25111</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>30760</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5204; 14235</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5513; 15761</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7267; 17120</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8077; 19316</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8505; 18707</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8734; 21004</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9096; 20351</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>10985; 26107</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>14994; 29053</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>15697; 31996</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>18008; 33180</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>22251; 42039</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>8018</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7136</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4061</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4537</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7967</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>8678</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>11296</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>15984</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>15814</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6868</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>15833</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>4268; 13269</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3660; 12219</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1471; 8148</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1967; 8845</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>4491; 13376</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4892; 14472</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>664; 6534</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>6326; 17433</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>10554; 22619</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>10818; 23347</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3386; 11679</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>9906; 23653</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>32961</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>48489</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>44723</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>38898</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>60252</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>75112</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>82468</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>99150</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>24799; 43228</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>38389; 61454</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>35753; 57727</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>28475; 49474</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>33619; 53681</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>40155; 62544</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>28107; 49225</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>48376; 76622</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>62450; 89395</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>82616; 114297</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>68339; 98708</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>82375; 117741</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 10,22</t>
+          <t>1,63; 9,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,32</t>
+          <t>1,2; 12,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 15,01</t>
+          <t>3,7; 16,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,94</t>
+          <t>2,43; 9,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 12,61</t>
+          <t>2,07; 12,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,69</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,57</t>
+          <t>0,0; 7,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,58</t>
+          <t>1,16; 6,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,33</t>
+          <t>2,85; 8,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,82</t>
+          <t>1,2; 6,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,0</t>
+          <t>2,12; 8,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,08</t>
+          <t>2,31; 6,77</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,65</t>
+          <t>0,99; 9,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 15,26</t>
+          <t>3,79; 15,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 12,66</t>
+          <t>3,69; 13,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,57</t>
+          <t>1,15; 8,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 15,84</t>
+          <t>4,07; 15,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 13,44</t>
+          <t>2,97; 12,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 10,32</t>
+          <t>1,87; 10,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 11,74</t>
+          <t>2,34; 11,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,84</t>
+          <t>3,44; 10,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 11,46</t>
+          <t>3,9; 11,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,52</t>
+          <t>3,45; 9,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,16</t>
+          <t>2,21; 7,69</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,57</t>
+          <t>1,24; 12,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 20,09</t>
+          <t>5,76; 18,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 19,55</t>
+          <t>4,28; 19,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 17,69</t>
+          <t>4,04; 16,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 9,63</t>
+          <t>2,22; 9,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 16,54</t>
+          <t>4,12; 16,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 10,73</t>
+          <t>1,18; 11,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,26</t>
+          <t>0,0; 7,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,67</t>
+          <t>2,36; 8,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 15,64</t>
+          <t>5,95; 15,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 11,95</t>
+          <t>3,79; 12,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,73</t>
+          <t>2,54; 9,7</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 8,28</t>
+          <t>2,32; 8,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 16,55</t>
+          <t>7,87; 17,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,77</t>
+          <t>4,93; 11,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,75</t>
+          <t>2,05; 7,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,22</t>
+          <t>2,57; 8,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 13,94</t>
+          <t>5,93; 14,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 10,8</t>
+          <t>4,32; 11,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 14,27</t>
+          <t>5,6; 14,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,2</t>
+          <t>3,07; 6,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 13,66</t>
+          <t>7,72; 13,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 10,07</t>
+          <t>5,45; 10,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 9,45</t>
+          <t>4,22; 9,47</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 20,73</t>
+          <t>7,71; 20,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 16,87</t>
+          <t>5,74; 16,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 16,85</t>
+          <t>6,93; 17,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,79; 16,24</t>
+          <t>7,11; 16,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,06; 22,13</t>
+          <t>10,04; 22,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 22,83</t>
+          <t>9,18; 21,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,17; 20,53</t>
+          <t>8,51; 20,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 16,05</t>
+          <t>6,7; 15,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 18,97</t>
+          <t>10,33; 19,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 17,25</t>
+          <t>8,7; 16,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,97; 16,53</t>
+          <t>9,0; 16,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,9; 14,93</t>
+          <t>8,05; 14,84</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,7; 17,72</t>
+          <t>6,13; 18,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,79; 22,67</t>
+          <t>6,6; 22,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 13,66</t>
+          <t>2,96; 13,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,84</t>
+          <t>2,76; 12,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 18,48</t>
+          <t>5,57; 18,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 19,55</t>
+          <t>6,27; 19,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,63</t>
+          <t>0,97; 10,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,79; 24,21</t>
+          <t>8,91; 25,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,36</t>
+          <t>7,46; 16,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,45; 18,25</t>
+          <t>8,23; 18,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,16</t>
+          <t>2,63; 9,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,03; 16,79</t>
+          <t>7,43; 16,92</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,62</t>
+          <t>4,96; 8,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,05; 12,88</t>
+          <t>8,18; 12,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,03</t>
+          <t>6,64; 10,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,58</t>
+          <t>4,45; 7,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,16</t>
+          <t>6,19; 10,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,64</t>
+          <t>7,34; 11,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,64</t>
+          <t>5,14; 8,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,25</t>
+          <t>6,38; 10,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,06; 8,68</t>
+          <t>6,04; 8,63</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 11,27</t>
+          <t>8,24; 11,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,03</t>
+          <t>6,2; 8,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 8,41</t>
+          <t>5,9; 8,42</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1305; 8224</t>
+          <t>1312; 7685</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>750; 6929</t>
+          <t>737; 7354</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2105; 9731</t>
+          <t>2400; 10538</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2605; 10307</t>
+          <t>2522; 10346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1990; 9035</t>
+          <t>1484; 8655</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4908</t>
+          <t>0; 4482</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5138</t>
+          <t>0; 5908</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1628; 8954</t>
+          <t>1582; 8795</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3755; 12668</t>
+          <t>4329; 13411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2042; 9178</t>
+          <t>1620; 9013</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3599; 12873</t>
+          <t>3033; 12108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5329; 16977</t>
+          <t>5538; 16237</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>665; 5943</t>
+          <t>683; 6647</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2175; 9976</t>
+          <t>2476; 10134</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2764; 10422</t>
+          <t>3036; 11292</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1075; 9016</t>
+          <t>1083; 7639</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2762; 10690</t>
+          <t>2744; 10710</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1952; 9211</t>
+          <t>2032; 8651</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2049; 9541</t>
+          <t>1728; 9764</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2341; 11128</t>
+          <t>2215; 10706</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4699; 13395</t>
+          <t>4686; 13803</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5227; 15348</t>
+          <t>5221; 15589</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5916; 16634</t>
+          <t>6021; 16446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4444; 15432</t>
+          <t>4181; 14543</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>783; 6739</t>
+          <t>725; 7115</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4411; 13367</t>
+          <t>3829; 12598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2153; 9623</t>
+          <t>2107; 9537</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1790; 8745</t>
+          <t>1998; 8324</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1306; 8084</t>
+          <t>1861; 7981</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2873; 11238</t>
+          <t>2802; 11295</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>817; 6549</t>
+          <t>717; 6810</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4634</t>
+          <t>0; 4828</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3395; 12329</t>
+          <t>3356; 11895</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8703; 21035</t>
+          <t>7998; 20213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3982; 13175</t>
+          <t>4173; 13598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2759; 11019</t>
+          <t>2873; 10985</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3513; 12468</t>
+          <t>3502; 12389</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10457; 22582</t>
+          <t>10745; 23495</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8206; 19507</t>
+          <t>8170; 19488</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4305; 14653</t>
+          <t>4447; 15543</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3832; 12218</t>
+          <t>3811; 12229</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10038; 22487</t>
+          <t>9565; 22880</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7265; 18451</t>
+          <t>7389; 19112</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13027; 31144</t>
+          <t>12214; 30938</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9356; 21544</t>
+          <t>9200; 20808</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24060; 40682</t>
+          <t>22989; 41428</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17906; 33905</t>
+          <t>18347; 34147</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18540; 41121</t>
+          <t>18359; 41232</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5204; 14235</t>
+          <t>5292; 14194</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5513; 15761</t>
+          <t>5368; 15159</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7267; 17120</t>
+          <t>7041; 17437</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8077; 19316</t>
+          <t>8460; 20028</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8505; 18707</t>
+          <t>8485; 18812</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8734; 21004</t>
+          <t>8446; 20039</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9096; 20351</t>
+          <t>8441; 20190</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10985; 26107</t>
+          <t>10891; 25901</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14994; 29053</t>
+          <t>15828; 29524</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15697; 31996</t>
+          <t>16144; 30885</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18008; 33180</t>
+          <t>18072; 33332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22251; 42039</t>
+          <t>22656; 41775</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4268; 13269</t>
+          <t>4589; 13700</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3660; 12219</t>
+          <t>3555; 12131</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1471; 8148</t>
+          <t>1768; 8340</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1967; 8845</t>
+          <t>1901; 8891</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4491; 13376</t>
+          <t>4029; 13159</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4892; 14472</t>
+          <t>4640; 14400</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>664; 6534</t>
+          <t>660; 6788</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6326; 17433</t>
+          <t>6417; 18163</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10554; 22619</t>
+          <t>10989; 23719</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10818; 23347</t>
+          <t>10528; 23244</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3386; 11679</t>
+          <t>3354; 11889</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9906; 23653</t>
+          <t>10462; 23835</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24799; 43228</t>
+          <t>24900; 42043</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38389; 61454</t>
+          <t>39011; 60340</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35753; 57727</t>
+          <t>34762; 56732</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28475; 49474</t>
+          <t>29011; 50213</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>33619; 53681</t>
+          <t>32699; 53374</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40155; 62544</t>
+          <t>39451; 62926</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28107; 49225</t>
+          <t>29264; 48765</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>48376; 76622</t>
+          <t>47707; 76573</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62450; 89395</t>
+          <t>62230; 88869</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>82616; 114297</t>
+          <t>83606; 114174</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68339; 98708</t>
+          <t>67788; 98104</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>82375; 117741</t>
+          <t>82549; 117880</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,34%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,88%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,07%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 9,55</t>
+          <t>2,75; 11,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 12,01</t>
+          <t>0,0; 6,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 16,25</t>
+          <t>0,0; 6,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 9,97</t>
+          <t>0,96; 6,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,08</t>
+          <t>1,59; 9,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,11</t>
+          <t>1,23; 11,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,55</t>
+          <t>3,3; 15,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,47</t>
+          <t>2,53; 10,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,82</t>
+          <t>2,74; 8,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,69</t>
+          <t>1,16; 6,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 8,46</t>
+          <t>2,28; 8,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,77</t>
+          <t>2,26; 6,56</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,13%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,68</t>
+          <t>4,09; 16,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 15,5</t>
+          <t>2,3; 12,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 13,72</t>
+          <t>1,85; 9,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 8,1</t>
+          <t>2,32; 11,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 15,87</t>
+          <t>0,98; 8,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 12,62</t>
+          <t>3,4; 16,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,57</t>
+          <t>3,62; 13,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 11,3</t>
+          <t>1,21; 9,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 10,14</t>
+          <t>3,46; 10,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 11,64</t>
+          <t>3,97; 11,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,41</t>
+          <t>3,35; 9,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 7,69</t>
+          <t>2,46; 8,21</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,89%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,68%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10,27%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 12,22</t>
+          <t>1,54; 9,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 18,94</t>
+          <t>4,28; 16,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 19,37</t>
+          <t>1,22; 11,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 16,84</t>
+          <t>0,0; 6,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 9,51</t>
+          <t>1,23; 11,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 16,62</t>
+          <t>6,44; 20,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,16</t>
+          <t>4,89; 19,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,56</t>
+          <t>3,49; 16,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,37</t>
+          <t>2,47; 8,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 15,03</t>
+          <t>6,51; 15,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 12,34</t>
+          <t>3,54; 12,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 9,7</t>
+          <t>2,13; 8,84</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,93%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,22</t>
+          <t>2,61; 8,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 17,22</t>
+          <t>6,03; 14,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,75</t>
+          <t>4,35; 11,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,16</t>
+          <t>5,55; 14,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,23</t>
+          <t>2,36; 8,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 14,18</t>
+          <t>8,07; 16,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 11,18</t>
+          <t>5,03; 12,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 14,17</t>
+          <t>2,36; 7,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,95</t>
+          <t>3,14; 7,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,91</t>
+          <t>7,77; 13,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,14</t>
+          <t>5,45; 10,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 9,47</t>
+          <t>4,77; 9,89</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13,87%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>13,05%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,12%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,18%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,45%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 20,67</t>
+          <t>10,47; 22,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 16,22</t>
+          <t>9,3; 22,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,93; 17,17</t>
+          <t>8,2; 20,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 16,84</t>
+          <t>5,99; 14,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,04; 22,25</t>
+          <t>7,69; 20,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 21,78</t>
+          <t>5,95; 16,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 20,36</t>
+          <t>6,88; 16,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 15,93</t>
+          <t>7,5; 17,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,33; 19,27</t>
+          <t>10,38; 19,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 16,65</t>
+          <t>8,58; 16,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 16,61</t>
+          <t>9,08; 16,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,05; 14,84</t>
+          <t>7,67; 13,54</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>10,71%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>13,24%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,13; 18,3</t>
+          <t>5,62; 17,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,6; 22,5</t>
+          <t>6,91; 20,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 13,99</t>
+          <t>0,99; 9,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,91</t>
+          <t>9,31; 24,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,57; 18,18</t>
+          <t>6,12; 17,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 19,45</t>
+          <t>6,41; 22,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,01</t>
+          <t>2,65; 13,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,91; 25,22</t>
+          <t>3,04; 13,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 16,11</t>
+          <t>7,04; 15,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,23; 18,17</t>
+          <t>8,13; 17,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 9,33</t>
+          <t>2,64; 9,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 16,92</t>
+          <t>7,28; 16,84</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6,57%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>8,55%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,19%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,38</t>
+          <t>6,3; 9,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,65</t>
+          <t>7,19; 11,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,84</t>
+          <t>5,15; 8,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,7</t>
+          <t>6,12; 9,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,1</t>
+          <t>4,84; 8,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 11,71</t>
+          <t>7,93; 12,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,56</t>
+          <t>6,74; 10,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,38; 10,24</t>
+          <t>4,78; 8,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,63</t>
+          <t>6,04; 8,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,26</t>
+          <t>8,24; 11,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,98</t>
+          <t>6,38; 8,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,42</t>
+          <t>5,97; 8,51</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4163</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3585</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3494</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2990</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5235</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5377</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4163</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1419</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1616</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9068</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1312; 7685</t>
+          <t>1970; 8448</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>737; 7354</t>
+          <t>0; 4576</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2400; 10538</t>
+          <t>0; 5394</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2522; 10346</t>
+          <t>1176; 7603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1484; 8655</t>
+          <t>1282; 7656</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4482</t>
+          <t>753; 7343</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5908</t>
+          <t>2142; 10364</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1582; 8795</t>
+          <t>2586; 10700</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4329; 13411</t>
+          <t>4174; 13313</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1620; 9013</t>
+          <t>1560; 9093</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3033; 12108</t>
+          <t>3262; 12167</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5538; 16237</t>
+          <t>5056; 14691</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5761</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4272</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4591</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2651</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5180</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5865</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3139</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5761</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4272</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8829</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>683; 6647</t>
+          <t>2763; 10859</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2476; 10134</t>
+          <t>1576; 8261</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3036; 11292</t>
+          <t>1707; 9111</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1083; 7639</t>
+          <t>2095; 10172</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2744; 10710</t>
+          <t>676; 6108</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2032; 8651</t>
+          <t>2222; 10658</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1728; 9764</t>
+          <t>2979; 11141</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2215; 10706</t>
+          <t>1164; 8807</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4686; 13803</t>
+          <t>4708; 14541</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5221; 15589</t>
+          <t>5318; 15721</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6021; 16446</t>
+          <t>5862; 16089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4181; 14543</t>
+          <t>4596; 15326</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3879</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2911</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2849</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7768</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5055</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3879</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6074</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2911</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5226</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>725; 7115</t>
+          <t>1296; 7868</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3829; 12598</t>
+          <t>2911; 11299</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2107; 9537</t>
+          <t>747; 7028</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1998; 8324</t>
+          <t>0; 3979</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1861; 7981</t>
+          <t>715; 6543</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2802; 11295</t>
+          <t>4285; 13335</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>717; 6810</t>
+          <t>2406; 9780</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4828</t>
+          <t>1758; 8066</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3356; 11895</t>
+          <t>3510; 11553</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7998; 20213</t>
+          <t>8754; 20558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4173; 13598</t>
+          <t>3898; 13701</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2873; 10985</t>
+          <t>2284; 9482</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7324</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15670</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12068</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18362</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6987</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15960</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>13149</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8335</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7324</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15670</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12068</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28559</t>
+          <t>26231</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3502; 12389</t>
+          <t>3870; 12204</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10745; 23495</t>
+          <t>9726; 23031</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8170; 19488</t>
+          <t>7432; 18803</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4447; 15543</t>
+          <t>11212; 28554</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3811; 12229</t>
+          <t>3550; 12704</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9565; 22880</t>
+          <t>11019; 22525</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7389; 19112</t>
+          <t>8348; 20672</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12214; 30938</t>
+          <t>4189; 13449</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9200; 20808</t>
+          <t>9395; 21722</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22989; 41428</t>
+          <t>23140; 41504</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18347; 34147</t>
+          <t>18347; 34973</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18359; 41232</t>
+          <t>18101; 37565</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13056</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13273</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13752</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14551</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>8963</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>9455</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>11358</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>13075</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13056</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13273</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30760</t>
+          <t>27838</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5292; 14194</t>
+          <t>8853; 19228</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5368; 15159</t>
+          <t>8560; 20731</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7041; 17437</t>
+          <t>8133; 20403</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8460; 20028</t>
+          <t>8882; 22098</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8485; 18812</t>
+          <t>5278; 14378</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8446; 20039</t>
+          <t>5562; 15414</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8441; 20190</t>
+          <t>6984; 17054</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10891; 25901</t>
+          <t>8867; 20150</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15828; 29524</t>
+          <t>15908; 30436</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16144; 30885</t>
+          <t>15912; 31113</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18072; 33332</t>
+          <t>18230; 33270</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22656; 41775</t>
+          <t>20431; 36085</t>
         </is>
       </c>
     </row>
@@ -2836,37 +2836,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7967</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8678</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10371</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>8018</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>7136</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>4061</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4537</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7967</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>8678</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2807</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11296</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15182</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4589; 13700</t>
+          <t>4069; 12931</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3555; 12131</t>
+          <t>5117; 14829</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1768; 8340</t>
+          <t>669; 6703</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1901; 8891</t>
+          <t>6355; 16758</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4029; 13159</t>
+          <t>4584; 13444</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4640; 14400</t>
+          <t>3457; 12089</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>660; 6788</t>
+          <t>1582; 8142</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6417; 18163</t>
+          <t>2141; 9297</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10989; 23719</t>
+          <t>10361; 22802</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10528; 23244</t>
+          <t>10401; 22718</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3354; 11889</t>
+          <t>3360; 12139</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10462; 23835</t>
+          <t>10094; 23351</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>61</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>53217</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>32961</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>48489</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>44723</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>38898</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>49386</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>37745</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99150</t>
+          <t>92375</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24900; 42043</t>
+          <t>33274; 52542</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39011; 60340</t>
+          <t>38642; 60799</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34762; 56732</t>
+          <t>29311; 48252</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29011; 50213</t>
+          <t>42117; 67462</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>32699; 53374</t>
+          <t>24258; 42601</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39451; 62926</t>
+          <t>37802; 59783</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29264; 48765</t>
+          <t>35270; 55792</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>47707; 76573</t>
+          <t>29391; 50383</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62230; 88869</t>
+          <t>62235; 89342</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>83606; 114174</t>
+          <t>83601; 114676</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>67788; 98104</t>
+          <t>69771; 96557</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>82549; 117880</t>
+          <t>77784; 110806</t>
         </is>
       </c>
     </row>
